--- a/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1_otu_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1_otu_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -26,9 +26,6 @@
     <t xml:space="preserve">MS_004</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_006</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_008</t>
   </si>
   <si>
@@ -56,6 +53,9 @@
     <t xml:space="preserve">MS_026</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_027</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_028</t>
   </si>
   <si>
@@ -104,6 +104,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t xml:space="preserve">MS_072</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_085</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_086</t>
   </si>
   <si>
@@ -314,9 +323,6 @@
     <t xml:space="preserve">MS_188</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_190</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_231</t>
   </si>
   <si>
@@ -428,6 +434,9 @@
     <t xml:space="preserve">MS_269</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_270</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_271</t>
   </si>
   <si>
@@ -437,28 +446,34 @@
     <t xml:space="preserve">MS_273</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_1126</t>
+    <t xml:space="preserve">Cluster_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_11</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_23</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_31</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_34</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_5</t>
@@ -1229,19 +1244,28 @@
       <c r="EK1" t="s">
         <v>140</v>
       </c>
+      <c r="EL1" t="s">
+        <v>141</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>142</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3227</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5579</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1259,28 +1283,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1261</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6196</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1558</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6714</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1307,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1349,16 +1373,16 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>3056</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1370,16 +1394,16 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1485</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2686</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>3365</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1532,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1634,30 +1658,39 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>3871</v>
       </c>
       <c r="EF2" t="n">
-        <v>0</v>
+        <v>1715</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>2109</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="EI2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0</v>
+        <v>5513</v>
       </c>
       <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -1672,325 +1705,325 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2085</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2677</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1029</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1078</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2269</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5511</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>103</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3935</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3120</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>738</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3706</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>260</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>626</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>1642</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>3422</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>516</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>56</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>2035</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>5810</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2029,19 +2062,19 @@
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
@@ -2077,12 +2110,21 @@
         <v>0</v>
       </c>
       <c r="EK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>45</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2094,19 +2136,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>738</v>
+        <v>56</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2154,16 +2196,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -2172,16 +2214,16 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -2199,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2292,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2364,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="n">
         <v>0</v>
@@ -2373,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CU4" t="n">
         <v>0</v>
@@ -2502,15 +2544,24 @@
         <v>0</v>
       </c>
       <c r="EK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3177</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2552,31 +2603,31 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2585,37 +2636,37 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1597</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2432</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>51</v>
+        <v>18898</v>
       </c>
       <c r="AF5" t="n">
-        <v>28</v>
+        <v>23829</v>
       </c>
       <c r="AG5" t="n">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1633</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1737</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2624,10 +2675,10 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2648,265 +2699,265 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
+        <v>7738</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>39</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>1673</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>21</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
         <v>43</v>
       </c>
-      <c r="AW5" t="n">
-        <v>89</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>73</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>305</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>124</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>127</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>117</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>243</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>211</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>172</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>86</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>65</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>163</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>167</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>531</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>90</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>993</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1509</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>138</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>199</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>92</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>172</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>141</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>271</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>788</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>636</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>541</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>890</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>793</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>235</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>123</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>35</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>72</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>196</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>231</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>202</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>581</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>681</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>330</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>775</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>265</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>0</v>
-      </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="EE5" t="n">
         <v>0</v>
@@ -2915,24 +2966,33 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
         <v>0</v>
       </c>
       <c r="EK5" t="n">
+        <v>87</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -2944,16 +3004,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>760</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3004,16 +3064,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -3022,22 +3082,22 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -3058,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3151,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3214,16 +3274,16 @@
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="CR6" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CU6" t="n">
         <v>0</v>
@@ -3352,12 +3412,21 @@
         <v>0</v>
       </c>
       <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -3372,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3414,55 +3483,55 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -3471,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1929</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -3495,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3549,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="BO7" t="n">
         <v>0</v>
@@ -3645,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>1446</v>
       </c>
       <c r="CT7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3660,10 +3729,10 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>0</v>
+        <v>3633</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>5089</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -3690,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
@@ -3699,16 +3768,16 @@
         <v>0</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>1324</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="DO7" t="n">
         <v>0</v>
@@ -3744,13 +3813,13 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
       <c r="EA7" t="n">
-        <v>0</v>
+        <v>1245</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="EC7" t="n">
         <v>0</v>
@@ -3778,11 +3847,20 @@
       </c>
       <c r="EK7" t="n">
         <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -3794,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3827,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -3860,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1597</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2432</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -3878,25 +3956,25 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1164</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1737</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -3908,10 +3986,10 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -3932,16 +4010,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
@@ -3953,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3965,10 +4043,10 @@
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
@@ -3998,19 +4076,19 @@
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -4019,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
@@ -4034,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="CH8" t="n">
         <v>0</v>
@@ -4052,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
@@ -4061,13 +4139,13 @@
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -4076,28 +4154,28 @@
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
@@ -4106,34 +4184,34 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="DO8" t="n">
         <v>0</v>
@@ -4142,40 +4220,40 @@
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="DR8" t="n">
         <v>0</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="EA8" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="EC8" t="n">
         <v>0</v>
@@ -4196,18 +4274,27 @@
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="EJ8" t="n">
         <v>0</v>
       </c>
       <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>21</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -4219,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -4228,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -4297,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4438,10 +4525,10 @@
         <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -4495,10 +4582,10 @@
         <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>0</v>
@@ -4621,18 +4708,27 @@
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
         <v>0</v>
       </c>
       <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -4647,37 +4743,37 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9494</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>9101</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>7915</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4184</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3059</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4932</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4371</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5424</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -4686,67 +4782,67 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3455</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3645</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1341</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2766</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2830</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2828</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>35791</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>53842</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>18643</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>28783</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>20006</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>29098</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>51239</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>51508</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>42229</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>41863</v>
+        <v>13</v>
       </c>
       <c r="AI10" t="n">
-        <v>14131</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12953</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3367</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2522</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -4758,10 +4854,10 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4114</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -4770,13 +4866,13 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1639</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>651</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -4797,10 +4893,10 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>964</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -4818,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>934</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>0</v>
@@ -4827,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
         <v>0</v>
@@ -4845,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
@@ -4914,22 +5010,22 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4819</v>
+        <v>0</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>45002</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>49019</v>
+        <v>332</v>
       </c>
       <c r="CU10" t="n">
-        <v>5014</v>
+        <v>193</v>
       </c>
       <c r="CV10" t="n">
-        <v>7231</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
         <v>0</v>
@@ -4944,10 +5040,10 @@
         <v>0</v>
       </c>
       <c r="DA10" t="n">
-        <v>1081</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
@@ -4965,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>5829</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -4974,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>5386</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -4989,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
@@ -5010,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
         <v>0</v>
@@ -5034,30 +5130,39 @@
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>1248</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>5189</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>2745</v>
+        <v>0</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>5813</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>5020</v>
+        <v>0</v>
       </c>
       <c r="EK10" t="n">
-        <v>2669</v>
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -5069,19 +5174,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I11" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -5114,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -5129,22 +5234,22 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -5153,251 +5258,251 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>10</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
         <v>5</v>
       </c>
-      <c r="AO11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>97</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>142</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>86</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>33</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>0</v>
-      </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
@@ -5405,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
@@ -5441,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="DY11" t="n">
-        <v>3195</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
         <v>0</v>
@@ -5477,12 +5582,21 @@
         <v>0</v>
       </c>
       <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -5494,28 +5608,28 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9494</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4320</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>9101</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>7915</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4184</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3059</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4932</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -5524,10 +5638,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4371</v>
       </c>
       <c r="P12" t="n">
-        <v>468</v>
+        <v>5424</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -5536,67 +5650,67 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3455</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3645</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="V12" t="n">
-        <v>250</v>
+        <v>2766</v>
       </c>
       <c r="W12" t="n">
-        <v>120</v>
+        <v>2830</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2828</v>
       </c>
       <c r="Y12" t="n">
-        <v>5443</v>
+        <v>35791</v>
       </c>
       <c r="Z12" t="n">
-        <v>5903</v>
+        <v>53842</v>
       </c>
       <c r="AA12" t="n">
-        <v>531</v>
+        <v>18643</v>
       </c>
       <c r="AB12" t="n">
-        <v>1234</v>
+        <v>28783</v>
       </c>
       <c r="AC12" t="n">
-        <v>12584</v>
+        <v>20006</v>
       </c>
       <c r="AD12" t="n">
-        <v>18432</v>
+        <v>29098</v>
       </c>
       <c r="AE12" t="n">
-        <v>35030</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>30247</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>313</v>
+        <v>51239</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>51508</v>
       </c>
       <c r="AI12" t="n">
-        <v>21002</v>
+        <v>42229</v>
       </c>
       <c r="AJ12" t="n">
-        <v>20482</v>
+        <v>41863</v>
       </c>
       <c r="AK12" t="n">
-        <v>17181</v>
+        <v>14131</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>12953</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>3367</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -5605,10 +5719,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>19893</v>
+        <v>2522</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12115</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5617,259 +5731,259 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4114</v>
       </c>
       <c r="AU12" t="n">
-        <v>381</v>
+        <v>1074</v>
       </c>
       <c r="AV12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>731</v>
+        <v>134</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1639</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="BA12" t="n">
-        <v>2195</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>4613</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2740</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3037</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>2748</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>8993</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>2084</v>
+        <v>964</v>
       </c>
       <c r="BH12" t="n">
-        <v>990</v>
+        <v>355</v>
       </c>
       <c r="BI12" t="n">
-        <v>4968</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>4744</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>2654</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>4987</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>7281</v>
+        <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>3190</v>
+        <v>934</v>
       </c>
       <c r="BO12" t="n">
-        <v>3603</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>11474</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="BR12" t="n">
-        <v>936</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>755</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>9260</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>1861</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>1069</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
-        <v>8467</v>
+        <v>871</v>
       </c>
       <c r="BX12" t="n">
-        <v>5325</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
         <v>0</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1048</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>7537</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>3438</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>5601</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>1328</v>
+        <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="CF12" t="n">
-        <v>8778</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>13603</v>
+        <v>0</v>
       </c>
       <c r="CH12" t="n">
-        <v>7625</v>
+        <v>0</v>
       </c>
       <c r="CI12" t="n">
-        <v>6481</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>2709</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>2634</v>
+        <v>0</v>
       </c>
       <c r="CM12" t="n">
-        <v>9022</v>
+        <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>8224</v>
+        <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>2922</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>3155</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>41159</v>
+        <v>0</v>
       </c>
       <c r="CR12" t="n">
-        <v>24706</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>81668</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>85143</v>
+        <v>4819</v>
       </c>
       <c r="CU12" t="n">
-        <v>3249</v>
+        <v>0</v>
       </c>
       <c r="CV12" t="n">
-        <v>4747</v>
+        <v>45002</v>
       </c>
       <c r="CW12" t="n">
-        <v>0</v>
+        <v>49019</v>
       </c>
       <c r="CX12" t="n">
-        <v>540</v>
+        <v>5014</v>
       </c>
       <c r="CY12" t="n">
-        <v>3071</v>
+        <v>7231</v>
       </c>
       <c r="CZ12" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="DA12" t="n">
-        <v>5520</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>4701</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>3750</v>
+        <v>1081</v>
       </c>
       <c r="DD12" t="n">
-        <v>3369</v>
+        <v>1013</v>
       </c>
       <c r="DE12" t="n">
-        <v>2002</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>4486</v>
+        <v>0</v>
       </c>
       <c r="DG12" t="n">
-        <v>5688</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>14643</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>7319</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>8090</v>
+        <v>5829</v>
       </c>
       <c r="DK12" t="n">
-        <v>8922</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>6019</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>4007</v>
+        <v>5386</v>
       </c>
       <c r="DN12" t="n">
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="DP12" t="n">
-        <v>6179</v>
+        <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6122</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>4928</v>
+        <v>515</v>
       </c>
       <c r="DS12" t="n">
-        <v>1481</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>5270</v>
+        <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>13297</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>5038</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>6866</v>
+        <v>0</v>
       </c>
       <c r="DY12" t="n">
-        <v>9762</v>
+        <v>2004</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2135</v>
+        <v>0</v>
       </c>
       <c r="EA12" t="n">
         <v>0</v>
@@ -5890,33 +6004,42 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>658</v>
+        <v>1248</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>5189</v>
       </c>
       <c r="EI12" t="n">
-        <v>871</v>
+        <v>2745</v>
       </c>
       <c r="EJ12" t="n">
         <v>0</v>
       </c>
       <c r="EK12" t="n">
-        <v>464</v>
+        <v>0</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>5813</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>5020</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>2669</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B13" t="n">
-        <v>2072</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3346</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5928,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -5940,34 +6063,34 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>841</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5759</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -5976,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -5985,37 +6108,37 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>10491</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>13346</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>52965</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>26861</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>744</v>
+        <v>6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -6024,19 +6147,19 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>248</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>412</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -6045,22 +6168,22 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>451</v>
+        <v>97</v>
       </c>
       <c r="AW13" t="n">
-        <v>1874</v>
+        <v>142</v>
       </c>
       <c r="AX13" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>411</v>
+        <v>86</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -6069,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -6084,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -6114,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -6135,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="BZ13" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
@@ -6150,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>2790</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -6210,13 +6333,13 @@
         <v>0</v>
       </c>
       <c r="CX13" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1656</v>
+        <v>0</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -6228,97 +6351,97 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>2910</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>3044</v>
+        <v>0</v>
       </c>
       <c r="DG13" t="n">
-        <v>5724</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
       </c>
       <c r="DK13" t="n">
-        <v>2619</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>1263</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DS13" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>775</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>1606</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="DY13" t="n">
-        <v>2472</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1441</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>3768</v>
+        <v>3195</v>
       </c>
       <c r="EB13" t="n">
-        <v>3907</v>
+        <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>3149</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>1485</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>1887</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="EH13" t="n">
-        <v>482</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
@@ -6327,12 +6450,21 @@
         <v>0</v>
       </c>
       <c r="EK13" t="n">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -6356,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -6377,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -6395,31 +6527,31 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>5443</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5903</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1234</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>12584</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>18432</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -6428,25 +6560,25 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>35030</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>30247</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>21002</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>20482</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>17181</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -6464,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>19893</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>12115</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
@@ -6479,16 +6611,16 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -6497,235 +6629,235 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4613</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2740</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>3037</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>2748</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>8993</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>2084</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>4968</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>4744</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>2654</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>4987</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>7281</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>3190</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>3603</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>11474</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>9260</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1861</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>8467</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>5325</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>7537</v>
       </c>
       <c r="CE14" t="n">
-        <v>0</v>
+        <v>3438</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>5601</v>
       </c>
       <c r="CG14" t="n">
-        <v>0</v>
+        <v>1328</v>
       </c>
       <c r="CH14" t="n">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>8778</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>13603</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>7625</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>6481</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>1561</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>2709</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>2634</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>9022</v>
       </c>
       <c r="CQ14" t="n">
-        <v>128</v>
+        <v>8224</v>
       </c>
       <c r="CR14" t="n">
-        <v>42</v>
+        <v>2922</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>3155</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>41159</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>24706</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>81668</v>
       </c>
       <c r="CW14" t="n">
-        <v>0</v>
+        <v>85143</v>
       </c>
       <c r="CX14" t="n">
-        <v>0</v>
+        <v>3249</v>
       </c>
       <c r="CY14" t="n">
-        <v>1</v>
+        <v>4747</v>
       </c>
       <c r="CZ14" t="n">
-        <v>7</v>
+        <v>540</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>3071</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>5520</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>4701</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>3369</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>2002</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>4486</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>5688</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>14643</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>7319</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>8090</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>8922</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>6019</v>
       </c>
       <c r="DO14" t="n">
-        <v>0</v>
+        <v>4007</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="DR14" t="n">
-        <v>0</v>
+        <v>6179</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>6122</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>4928</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>1481</v>
       </c>
       <c r="DV14" t="n">
-        <v>2</v>
+        <v>5270</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>13297</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>5038</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>6866</v>
       </c>
       <c r="EA14" t="n">
-        <v>0</v>
+        <v>9762</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>2135</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
@@ -6746,27 +6878,36 @@
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="EJ14" t="n">
         <v>0</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>871</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>464</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2072</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3346</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6787,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -6802,22 +6943,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5759</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -6826,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -6835,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>10491</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>13346</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -6853,330 +6994,1207 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
+        <v>52965</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>26861</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>744</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>745</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>747</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>248</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>412</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>451</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1874</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>575</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>411</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>626</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>309</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>31</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>786</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>162</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>2790</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1261</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1656</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>130</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2910</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>3044</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>5724</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>915</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>686</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>2619</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>1263</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>44</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>22</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>100</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>275</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>775</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>580</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>383</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>1606</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>273</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>2472</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>1441</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>3768</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>3907</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>3149</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>1485</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>1887</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>250</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>482</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>128</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>42</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
         <v>3037</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AL17" t="n">
         <v>3128</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AM17" t="n">
         <v>19</v>
       </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
         <v>1979</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BB17" t="n">
         <v>4623</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BC17" t="n">
         <v>792</v>
       </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>1217</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BK17" t="n">
         <v>2975</v>
       </c>
-      <c r="BI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS15" t="n">
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
         <v>442</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="BW17" t="n">
         <v>619</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="BX17" t="n">
         <v>6732</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="BY17" t="n">
         <v>5863</v>
       </c>
-      <c r="BW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ15" t="n">
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
         <v>108</v>
       </c>
-      <c r="CA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ15" t="n">
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
         <v>4315</v>
       </c>
-      <c r="CK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM15" t="n">
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
         <v>4306</v>
       </c>
-      <c r="CN15" t="n">
+      <c r="CQ17" t="n">
         <v>401</v>
       </c>
-      <c r="CO15" t="n">
+      <c r="CR17" t="n">
         <v>311</v>
       </c>
-      <c r="CP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU15" t="n">
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
         <v>2965</v>
       </c>
-      <c r="CV15" t="n">
+      <c r="CY17" t="n">
         <v>4755</v>
       </c>
-      <c r="CW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX15" t="n">
+      <c r="CZ17" t="n">
         <v>3322</v>
       </c>
-      <c r="CY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ15" t="n">
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
         <v>124</v>
       </c>
-      <c r="DA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC15" t="n">
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
         <v>750</v>
       </c>
-      <c r="DD15" t="n">
+      <c r="DF17" t="n">
         <v>548</v>
       </c>
-      <c r="DE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF15" t="n">
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
         <v>2379</v>
       </c>
-      <c r="DG15" t="n">
+      <c r="DI17" t="n">
         <v>3981</v>
       </c>
-      <c r="DH15" t="n">
+      <c r="DJ17" t="n">
         <v>1213</v>
       </c>
-      <c r="DI15" t="n">
+      <c r="DK17" t="n">
         <v>8559</v>
       </c>
-      <c r="DJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO15" t="n">
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
         <v>3110</v>
       </c>
-      <c r="DP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS15" t="n">
+      <c r="DR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
         <v>2069</v>
       </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
         <v>1619</v>
       </c>
-      <c r="DV15" t="n">
+      <c r="DX17" t="n">
         <v>1790</v>
       </c>
-      <c r="DW15" t="n">
+      <c r="DY17" t="n">
         <v>7317</v>
       </c>
-      <c r="DX15" t="n">
+      <c r="DZ17" t="n">
         <v>1276</v>
       </c>
-      <c r="DY15" t="n">
+      <c r="EA17" t="n">
         <v>94</v>
       </c>
-      <c r="DZ15" t="n">
+      <c r="EB17" t="n">
         <v>1670</v>
       </c>
-      <c r="EA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI15" t="n">
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
         <v>71</v>
       </c>
-      <c r="EJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK15" t="n">
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
         <v>0</v>
       </c>
     </row>
